--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D646DEF-FF4C-4017-9D19-04AB3862D6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A4949E-44E1-4FE0-BAA2-2A17F490AE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="160">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -712,6 +712,44 @@
     <rPh sb="0" eb="2">
       <t>ケツジョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>欠場</t>
+    <rPh sb="0" eb="2">
+      <t>ケツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セプテンバーセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エレガントルビー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベルキューティ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラッキーレディ25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴッドクインビー25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シャドウライフ25</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -878,7 +916,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -949,6 +987,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1823,6 +1864,10 @@
       <c r="I21" s="4">
         <v>2700</v>
       </c>
+      <c r="K21" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="L21" s="15"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="3" t="s">
@@ -1843,6 +1888,12 @@
       <c r="I22" s="4">
         <v>600</v>
       </c>
+      <c r="K22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1700</v>
+      </c>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="3" t="s">
@@ -1863,6 +1914,12 @@
       <c r="I23" s="4">
         <v>5400</v>
       </c>
+      <c r="K23" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="3" t="s">
@@ -1884,6 +1941,12 @@
       <c r="I24" s="4" t="s">
         <v>150</v>
       </c>
+      <c r="K24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L24" s="4">
+        <v>690</v>
+      </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="3" t="s">
@@ -1898,6 +1961,12 @@
       <c r="I25" s="4">
         <v>600</v>
       </c>
+      <c r="K25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" s="4">
+        <v>1850</v>
+      </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
@@ -1916,6 +1985,12 @@
       <c r="I26" s="4">
         <v>3500</v>
       </c>
+      <c r="K26" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="L26" s="4">
+        <v>1050</v>
+      </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
@@ -1933,6 +2008,13 @@
       </c>
       <c r="I27" s="4">
         <v>3000</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L27" s="6">
+        <f>AVERAGE(L22:L26)</f>
+        <v>1322.5</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A4949E-44E1-4FE0-BAA2-2A17F490AE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2539939E-ED54-473D-A261-F1E953C71C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="163">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -756,6 +756,21 @@
     <t>欠場</t>
     <rPh sb="0" eb="2">
       <t>ケツジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オータムセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シンシアリダーリン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -796,7 +811,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -836,6 +851,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,7 +937,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -989,7 +1010,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1914,7 +1938,7 @@
       <c r="I23" s="4">
         <v>5400</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="K23" s="3" t="s">
         <v>158</v>
       </c>
       <c r="L23" s="4" t="s">
@@ -2056,6 +2080,10 @@
       <c r="I29" s="4">
         <v>1700</v>
       </c>
+      <c r="K29" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="L29" s="25"/>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
@@ -2076,6 +2104,12 @@
       <c r="I30" s="4">
         <v>620</v>
       </c>
+      <c r="K30" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="L30" s="4">
+        <v>1250</v>
+      </c>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
@@ -2095,6 +2129,12 @@
       </c>
       <c r="I31" s="4">
         <v>2400</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L31" s="6">
+        <v>1250</v>
       </c>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">

--- a/エフフォーリア産駒 セリ結果.xlsx
+++ b/エフフォーリア産駒 セリ結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eff_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2539939E-ED54-473D-A261-F1E953C71C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6F1880-BDB2-4C4B-9914-B9DB517F1E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2EAD33F1-2394-4654-94C6-8653E5CCB6CF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="168">
   <si>
     <t>馬名</t>
     <rPh sb="0" eb="2">
@@ -765,6 +765,29 @@
   </si>
   <si>
     <t>シンシアリダーリン25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミックスセール2026</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トゥリフォー26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レッドティー26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リヴィア26</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1004,16 +1027,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1722,10 +1745,14 @@
       <c r="I14" s="4">
         <v>1100</v>
       </c>
-      <c r="K14" s="22" t="s">
+      <c r="K14" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="L14" s="23"/>
+      <c r="L14" s="25"/>
+      <c r="N14" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="O14" s="17"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="3" t="s">
@@ -1752,6 +1779,12 @@
       <c r="L15" s="4" t="s">
         <v>84</v>
       </c>
+      <c r="N15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="O15" s="4">
+        <v>8400</v>
+      </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="3" t="s">
@@ -1778,8 +1811,14 @@
       <c r="L16" s="4">
         <v>1650</v>
       </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="N16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="O16" s="4">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1805,8 +1844,14 @@
       <c r="L17" s="4">
         <v>2400</v>
       </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="N17" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="O17" s="4">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1825,8 +1870,15 @@
       <c r="L18" s="4">
         <v>530</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="N18" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="O18" s="6">
+        <f>AVERAGE(O15:O17)</f>
+        <v>7866.666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1851,7 +1903,7 @@
         <v>1526.6666666666667</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1869,7 +1921,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1893,7 +1945,7 @@
       </c>
       <c r="L21" s="15"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
@@ -1919,7 +1971,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1945,7 +1997,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
@@ -1972,7 +2024,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
@@ -1992,7 +2044,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
@@ -2016,7 +2068,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
@@ -2041,7 +2093,7 @@
         <v>1322.5</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
@@ -2061,7 +2113,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
         <v>26</v>
       </c>
@@ -2080,12 +2132,12 @@
       <c r="I29" s="4">
         <v>1700</v>
       </c>
-      <c r="K29" s="24" t="s">
+      <c r="K29" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="L29" s="25"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
         <v>27</v>
       </c>
@@ -2111,7 +2163,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
         <v>28</v>
       </c>
@@ -2137,7 +2189,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
         <v>29</v>
       </c>
